--- a/sample_data/sample_multi_sheet_workbook.xlsx
+++ b/sample_data/sample_multi_sheet_workbook.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,50 +435,55 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Reference 1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Post Date</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Effective Date</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Matched/Unmatched</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Reference 10</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Reference 9</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Reference 7</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -498,16 +503,14 @@
       <c r="C2" t="n">
         <v>1000</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>SAMPLE001</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>2026-08-03</t>
@@ -515,31 +518,36 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>SYSTEM</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>Matched</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>FAST</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>5801</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
@@ -559,16 +567,14 @@
       <c r="C3" t="n">
         <v>250</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="n">
+        <v>-250</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>SAMPLE002</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-08-03</t>
@@ -576,31 +582,36 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>SYSTEM</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>Matched</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>FAST</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2105</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
@@ -609,7 +620,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -618,18 +629,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-75</v>
-      </c>
-      <c r="D4" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="D4" t="n">
+        <v>75</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>SAMPLE003</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-08-03</t>
@@ -637,31 +646,36 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>SYSTEM</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>Matched</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>FAST</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>DEDU</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
@@ -681,16 +695,14 @@
       <c r="C5" t="n">
         <v>500</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="n">
+        <v>500</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>SAMPLE004</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-03</t>
@@ -698,31 +710,36 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>SYSTEM</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>Matched</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>FAST</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>CHKD</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
@@ -742,16 +759,14 @@
       <c r="C6" t="n">
         <v>2000</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>SAMPLE005</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-04</t>
@@ -759,31 +774,36 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>SYSTEM</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>Matched</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>FAST</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>5801</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
@@ -803,16 +823,14 @@
       <c r="C7" t="n">
         <v>300</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="n">
+        <v>-300</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>SAMPLE006</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-08-04</t>
@@ -820,31 +838,36 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>SYSTEM</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>Matched</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>FAST</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>SJ90</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
@@ -864,52 +887,55 @@
       <c r="C8" t="n">
         <v>150</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="n">
+        <v>-150</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>SAMPLE007</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>SYSTEM</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>Unmatched</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>GDS</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>5801</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Treasury</t>
         </is>
@@ -929,48 +955,51 @@
       <c r="C9" t="n">
         <v>900</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" t="n">
+        <v>-900</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>SAMPLE008</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>SYSTEM</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Matched</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>FAST</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>5801</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
@@ -990,16 +1019,14 @@
       <c r="C10" t="n">
         <v>120</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="n">
+        <v>120</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>SAMPLE009</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-08-03</t>
@@ -1007,35 +1034,40 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>SYSTEM</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>Matched</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>GDS</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>5801</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Treasury</t>
         </is>
@@ -1053,18 +1085,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-60</v>
-      </c>
-      <c r="D11" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="D11" t="n">
+        <v>60</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>SAMPLE010</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-04</t>
@@ -1072,35 +1102,40 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>SYSTEM</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>Matched</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>GDS</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>5801</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Treasury</t>
         </is>
@@ -1118,18 +1153,16 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>300</v>
+      </c>
+      <c r="D12" t="n">
         <v>-300</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>SAMPLE011</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-08-04</t>
@@ -1137,35 +1170,40 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>SYSTEM</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>Matched</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>GDS</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>5801</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Treasury</t>
         </is>
@@ -1185,16 +1223,14 @@
       <c r="C13" t="n">
         <v>75</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="n">
+        <v>75</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>SAMPLE012</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-04</t>
@@ -1202,31 +1238,36 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>SYSTEM</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>Matched</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>FAST</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>BRCR</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
@@ -1244,50 +1285,53 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D14" t="n">
         <v>-1000</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>SAMPLE013</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>SYSTEM</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>FAST</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>WIRE</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
@@ -1307,48 +1351,51 @@
       <c r="C15" t="n">
         <v>500</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="n">
+        <v>500</v>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>SAMPLE014</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>SYSTEM</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>FAST</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>INCO</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
